--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SUMIALKI CB CIUDAD DE MOSTOLES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SUMIALKI CB CIUDAD DE MOSTOLES.xlsx
@@ -565,13 +565,13 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1023</v>
+        <v>7.4396</v>
       </c>
       <c r="E2" t="n">
-        <v>27.4072</v>
+        <v>19.6852</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.3047</v>
+        <v>-12.2457</v>
       </c>
       <c r="G2" t="n">
         <v>3.469500000000001</v>
@@ -610,13 +610,13 @@
         <v>12.55</v>
       </c>
       <c r="S2" t="n">
-        <v>6.5531</v>
+        <v>-2.1098</v>
       </c>
       <c r="T2" t="n">
-        <v>8.628</v>
+        <v>0.9058999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.0751</v>
+        <v>-3.016</v>
       </c>
       <c r="V2" t="n">
         <v>10.5206</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GOMEZ ALONSO</t>
+          <t>G. COMACHIO COACHMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2533</v>
+        <v>1.1962</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.18</v>
+        <v>-0.3777</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0732</v>
+        <v>1.5738</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2974</v>
+        <v>-3.6863</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-3.243</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2283</v>
+        <v>-0.4433</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0407</v>
+        <v>1.298</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>0.6760999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3381</v>
+        <v>-4.9843</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-3.865</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.269</v>
+        <v>-1.1192</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>5.2131</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.5447</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3862</v>
+        <v>6.7578</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3421</v>
+        <v>-1.1584</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2207</v>
+        <v>-0.622</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1213</v>
+        <v>-0.5365</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8278</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.491</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3366999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. COMACHIO COACHMAN</t>
+          <t>M. GOMEZ ALONSO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.5789</v>
+        <v>-0.2284</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.9359</v>
+        <v>-0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>0.357</v>
+        <v>-0.0484</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.6863</v>
+        <v>-0.2974</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.243</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4433</v>
+        <v>-0.2283</v>
       </c>
       <c r="J4" t="n">
-        <v>1.298</v>
+        <v>0.0407</v>
       </c>
       <c r="K4" t="n">
-        <v>0.622</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6760999999999999</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.9843</v>
+        <v>-0.3381</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.865</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1192</v>
+        <v>-0.269</v>
       </c>
       <c r="P4" t="n">
-        <v>5.2131</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5447</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>6.7578</v>
+        <v>0.3862</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.9336</v>
+        <v>-0.3172</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.1804</v>
+        <v>-0.2207</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.7531</v>
+        <v>-0.0965</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8278</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.491</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3366999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2557</v>
+        <v>-2.0282</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5728</v>
+        <v>-1.4694</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.5588</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7042</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5517</v>
+        <v>-0.324</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2759</v>
+        <v>-0.1725</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2758</v>
+        <v>-0.1515</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.0399</v>
+        <v>-2.393799999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>2.319800000000001</v>
+        <v>5.332699999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.3595</v>
+        <v>-7.726800000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3212999999999999</v>
@@ -922,13 +922,13 @@
         <v>18.5355</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.9633</v>
+        <v>-3.3171</v>
       </c>
       <c r="T6" t="n">
-        <v>-6.21</v>
+        <v>-3.1968</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2467</v>
+        <v>-0.1204000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>6.2647</v>
@@ -955,13 +955,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.8178</v>
+        <v>-7.088200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5474</v>
+        <v>-3.9059</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2704</v>
+        <v>-3.1823</v>
       </c>
       <c r="G7" t="n">
         <v>-5.251799999999999</v>
@@ -1000,13 +1000,13 @@
         <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2539</v>
+        <v>-0.5243</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1373</v>
+        <v>-0.2212</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3913</v>
+        <v>-0.303</v>
       </c>
       <c r="V7" t="n">
         <v>-2.0845</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARENAS CUESTA</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>-13.0521</v>
+        <v>-8.439499999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.0327</v>
+        <v>18.47499999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0195</v>
+        <v>-26.9149</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.3896</v>
+        <v>13.8832</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.207</v>
+        <v>-20.8452</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1823</v>
+        <v>34.7285</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.2347</v>
+        <v>66.0596</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.8949</v>
+        <v>12.7647</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6602</v>
+        <v>53.2949</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1547</v>
+        <v>-52.1765</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.312</v>
+        <v>-33.61</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8425</v>
+        <v>-18.5665</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.703</v>
+        <v>-31.4717</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.9855</v>
+        <v>-78.5827</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2824</v>
+        <v>47.1111</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.1099</v>
+        <v>-14.9283</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.897</v>
+        <v>-8.307399999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2127</v>
+        <v>-6.6212</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1502</v>
+        <v>24.0771</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0845</v>
+        <v>39.3057</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06560000000000001</v>
+        <v>-15.2286</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>J. ARENAS CUESTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.356</v>
+        <v>-11.5281</v>
       </c>
       <c r="E9" t="n">
-        <v>11.7939</v>
+        <v>-10.8812</v>
       </c>
       <c r="F9" t="n">
-        <v>-26.15</v>
+        <v>-0.6469999999999998</v>
       </c>
       <c r="G9" t="n">
-        <v>13.8832</v>
+        <v>-8.3896</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.8452</v>
+        <v>-7.207</v>
       </c>
       <c r="I9" t="n">
-        <v>34.7285</v>
+        <v>-1.1823</v>
       </c>
       <c r="J9" t="n">
-        <v>66.0596</v>
+        <v>-5.2347</v>
       </c>
       <c r="K9" t="n">
-        <v>12.7647</v>
+        <v>-5.8949</v>
       </c>
       <c r="L9" t="n">
-        <v>53.2949</v>
+        <v>0.6602</v>
       </c>
       <c r="M9" t="n">
-        <v>-52.1765</v>
+        <v>-3.1547</v>
       </c>
       <c r="N9" t="n">
-        <v>-33.61</v>
+        <v>-1.312</v>
       </c>
       <c r="O9" t="n">
-        <v>-18.5665</v>
+        <v>-1.8425</v>
       </c>
       <c r="P9" t="n">
-        <v>-31.4717</v>
+        <v>-2.703</v>
       </c>
       <c r="Q9" t="n">
-        <v>-78.5827</v>
+        <v>-5.9855</v>
       </c>
       <c r="R9" t="n">
-        <v>47.1111</v>
+        <v>3.2824</v>
       </c>
       <c r="S9" t="n">
-        <v>-20.8449</v>
+        <v>-2.5859</v>
       </c>
       <c r="T9" t="n">
-        <v>-14.989</v>
+        <v>-1.7455</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.856199999999999</v>
+        <v>-0.8403</v>
       </c>
       <c r="V9" t="n">
-        <v>24.0771</v>
+        <v>2.1502</v>
       </c>
       <c r="W9" t="n">
-        <v>39.3057</v>
+        <v>2.0845</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.2286</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>L. SIBENIK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-18.1585</v>
+        <v>-18.0068</v>
       </c>
       <c r="E10" t="n">
-        <v>2.075</v>
+        <v>-8.7324</v>
       </c>
       <c r="F10" t="n">
-        <v>-20.2334</v>
+        <v>-9.2746</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.605599999999999</v>
+        <v>-19.361</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.1399</v>
+        <v>-20.4918</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4658</v>
+        <v>1.130699999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>5.4234</v>
+        <v>-0.03049999999999997</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8647</v>
+        <v>-3.931</v>
       </c>
       <c r="L10" t="n">
-        <v>3.5587</v>
+        <v>3.9007</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.0289</v>
+        <v>-19.3305</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.0044</v>
+        <v>-16.5606</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.0243</v>
+        <v>-2.7699</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4756</v>
+        <v>7.3371</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.5647</v>
+        <v>-10.6195</v>
       </c>
       <c r="R10" t="n">
-        <v>10.0401</v>
+        <v>17.9563</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.5981</v>
+        <v>-3.2762</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1897999999999997</v>
+        <v>-0.37</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.788</v>
+        <v>-2.9059</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.430299999999999</v>
+        <v>-2.7069</v>
       </c>
       <c r="W10" t="n">
-        <v>3.0266</v>
+        <v>2.2874</v>
       </c>
       <c r="X10" t="n">
-        <v>-11.4568</v>
+        <v>-4.9943</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SOTO MADRIGAL</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.1707</v>
+        <v>-19.3603</v>
       </c>
       <c r="E11" t="n">
-        <v>4.095300000000001</v>
+        <v>-0.6553999999999995</v>
       </c>
       <c r="F11" t="n">
-        <v>-22.266</v>
+        <v>-18.7051</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.393</v>
+        <v>-9.605599999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-13.4571</v>
+        <v>-6.1399</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9360999999999993</v>
+        <v>-3.4658</v>
       </c>
       <c r="J11" t="n">
-        <v>8.173999999999999</v>
+        <v>5.4234</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7244</v>
+        <v>1.8647</v>
       </c>
       <c r="L11" t="n">
-        <v>4.4496</v>
+        <v>3.5587</v>
       </c>
       <c r="M11" t="n">
-        <v>-22.5675</v>
+        <v>-15.0289</v>
       </c>
       <c r="N11" t="n">
-        <v>-17.1817</v>
+        <v>-8.0044</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.385899999999999</v>
+        <v>-7.0243</v>
       </c>
       <c r="P11" t="n">
-        <v>9.0746</v>
+        <v>3.4756</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.8125</v>
+        <v>-6.5647</v>
       </c>
       <c r="R11" t="n">
-        <v>19.887</v>
+        <v>10.0401</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2966</v>
+        <v>-4.7999</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8076</v>
+        <v>-2.5404</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.5106</v>
+        <v>-2.2594</v>
       </c>
       <c r="V11" t="n">
-        <v>-13.1492</v>
+        <v>-8.430299999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>3.9261</v>
+        <v>3.0266</v>
       </c>
       <c r="X11" t="n">
-        <v>-17.0752</v>
+        <v>-11.4568</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SIBENIK</t>
+          <t>D. SOTO MADRIGAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.7642</v>
+        <v>-19.5301</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.7532</v>
+        <v>2.3719</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.0109</v>
+        <v>-21.902</v>
       </c>
       <c r="G12" t="n">
-        <v>-19.361</v>
+        <v>-14.393</v>
       </c>
       <c r="H12" t="n">
-        <v>-20.4918</v>
+        <v>-13.4571</v>
       </c>
       <c r="I12" t="n">
-        <v>1.130699999999999</v>
+        <v>-0.9360999999999993</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.03049999999999997</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.931</v>
+        <v>3.7244</v>
       </c>
       <c r="L12" t="n">
-        <v>3.9007</v>
+        <v>4.4496</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.3305</v>
+        <v>-22.5675</v>
       </c>
       <c r="N12" t="n">
-        <v>-16.5606</v>
+        <v>-17.1817</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.7699</v>
+        <v>-5.385899999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>7.3371</v>
+        <v>9.0746</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.6195</v>
+        <v>-10.8125</v>
       </c>
       <c r="R12" t="n">
-        <v>17.9563</v>
+        <v>19.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.0335</v>
+        <v>-1.0626</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3909000000000001</v>
+        <v>1.0845</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.6426</v>
+        <v>-2.1466</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7069</v>
+        <v>-13.1492</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2874</v>
+        <v>3.9261</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.9943</v>
+        <v>-17.0752</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.9638</v>
+        <v>-22.1126</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6526</v>
+        <v>-6.252300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.311</v>
+        <v>-15.8602</v>
       </c>
       <c r="G13" t="n">
         <v>-20.1171</v>
@@ -1468,13 +1468,13 @@
         <v>21.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.8786</v>
+        <v>-3.0274</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2816000000000001</v>
+        <v>-0.8813</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.5969</v>
+        <v>-2.146</v>
       </c>
       <c r="V13" t="n">
         <v>-4.181</v>
@@ -1501,13 +1501,13 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.7133</v>
+        <v>-22.6554</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.2252</v>
+        <v>-17.0115</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.488</v>
+        <v>-5.6438</v>
       </c>
       <c r="G14" t="n">
         <v>-23.9174</v>
@@ -1546,13 +1546,13 @@
         <v>8.4955</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.305899999999999</v>
+        <v>-4.2479</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6986</v>
+        <v>-2.485</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6073</v>
+        <v>-1.7627</v>
       </c>
       <c r="V14" t="n">
         <v>6.088900000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-29.2475</v>
+        <v>-27.9925</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.2412</v>
+        <v>-6.288900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.0059</v>
+        <v>-21.7035</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.2942</v>
+        <v>-15.5148</v>
       </c>
       <c r="H15" t="n">
-        <v>-11.3947</v>
+        <v>-20.4528</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.8991</v>
+        <v>4.937800000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.6628</v>
+        <v>19.6995</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4915999999999999</v>
+        <v>3.6293</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.1712</v>
+        <v>16.0704</v>
       </c>
       <c r="M15" t="n">
-        <v>-11.6315</v>
+        <v>-35.2147</v>
       </c>
       <c r="N15" t="n">
-        <v>-10.903</v>
+        <v>-24.0819</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7283999999999999</v>
+        <v>-11.1327</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5103</v>
+        <v>-6.9506</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.9164</v>
+        <v>-33.596</v>
       </c>
       <c r="R15" t="n">
-        <v>10.4263</v>
+        <v>26.6445</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.7898</v>
+        <v>-10.4061</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.1756</v>
+        <v>-4.2888</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.614</v>
+        <v>-6.1172</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.6739</v>
+        <v>4.8791</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5133</v>
+        <v>11.8958</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.187200000000001</v>
+        <v>-7.016500000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-33.177</v>
+        <v>-28.6434</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.4816</v>
+        <v>-16.4343</v>
       </c>
       <c r="F16" t="n">
-        <v>-23.6952</v>
+        <v>-12.2087</v>
       </c>
       <c r="G16" t="n">
-        <v>-15.5148</v>
+        <v>-18.2942</v>
       </c>
       <c r="H16" t="n">
-        <v>-20.4528</v>
+        <v>-11.3947</v>
       </c>
       <c r="I16" t="n">
-        <v>4.937800000000001</v>
+        <v>-6.8991</v>
       </c>
       <c r="J16" t="n">
-        <v>19.6995</v>
+        <v>-6.6628</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6293</v>
+        <v>-0.4915999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>16.0704</v>
+        <v>-6.1712</v>
       </c>
       <c r="M16" t="n">
-        <v>-35.2147</v>
+        <v>-11.6315</v>
       </c>
       <c r="N16" t="n">
-        <v>-24.0819</v>
+        <v>-10.903</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.1327</v>
+        <v>-0.7283999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-6.9506</v>
+        <v>2.5103</v>
       </c>
       <c r="Q16" t="n">
-        <v>-33.596</v>
+        <v>-7.9164</v>
       </c>
       <c r="R16" t="n">
-        <v>26.6445</v>
+        <v>10.4263</v>
       </c>
       <c r="S16" t="n">
-        <v>-15.5901</v>
+        <v>-7.1855</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.4815</v>
+        <v>-3.3688</v>
       </c>
       <c r="U16" t="n">
-        <v>-8.1089</v>
+        <v>-3.8168</v>
       </c>
       <c r="V16" t="n">
-        <v>4.8791</v>
+        <v>-5.6739</v>
       </c>
       <c r="W16" t="n">
-        <v>11.8958</v>
+        <v>1.5133</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.016500000000001</v>
+        <v>-7.187200000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-37.4152</v>
+        <v>-43.9457</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.8647</v>
+        <v>-18.2291</v>
       </c>
       <c r="F17" t="n">
-        <v>-23.5505</v>
+        <v>-25.7167</v>
       </c>
       <c r="G17" t="n">
         <v>-20.9256</v>
@@ -1780,13 +1780,13 @@
         <v>21.2386</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6487</v>
+        <v>-3.8818</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9512</v>
+        <v>-2.4131</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6974000000000004</v>
+        <v>-1.4686</v>
       </c>
       <c r="V17" t="n">
         <v>-16.8212</v>
@@ -1813,13 +1813,13 @@
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-48.0144</v>
+        <v>-49.1149</v>
       </c>
       <c r="E18" t="n">
-        <v>-24.6545</v>
+        <v>-26.5572</v>
       </c>
       <c r="F18" t="n">
-        <v>-23.36</v>
+        <v>-22.5578</v>
       </c>
       <c r="G18" t="n">
         <v>-30.6662</v>
@@ -1858,13 +1858,13 @@
         <v>16.2185</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.2509</v>
+        <v>-7.3509</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.97</v>
+        <v>-2.8728</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.2808</v>
+        <v>-4.4781</v>
       </c>
       <c r="V18" t="n">
         <v>-9.166700000000001</v>
@@ -1891,13 +1891,13 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>-54.6387</v>
+        <v>-55.0921</v>
       </c>
       <c r="E19" t="n">
-        <v>-36.8602</v>
+        <v>-38.0805</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.7785</v>
+        <v>-17.0118</v>
       </c>
       <c r="G19" t="n">
         <v>-30.3847</v>
@@ -1936,13 +1936,13 @@
         <v>27.2241</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.7602</v>
+        <v>-6.2138</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1661</v>
+        <v>-2.3864</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.593999999999999</v>
+        <v>-3.8273</v>
       </c>
       <c r="V19" t="n">
         <v>2.5518</v>
@@ -1969,13 +1969,13 @@
         <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>-78.5719</v>
+        <v>-70.6812</v>
       </c>
       <c r="E20" t="n">
-        <v>-50.7319</v>
+        <v>-44.5398</v>
       </c>
       <c r="F20" t="n">
-        <v>-27.8405</v>
+        <v>-26.1412</v>
       </c>
       <c r="G20" t="n">
         <v>-24.6016</v>
@@ -2014,13 +2014,13 @@
         <v>31.0855</v>
       </c>
       <c r="S20" t="n">
-        <v>-20.8963</v>
+        <v>-13.0055</v>
       </c>
       <c r="T20" t="n">
-        <v>-12.3378</v>
+        <v>-6.1457</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.5586</v>
+        <v>-6.859599999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-4.6914</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-97.56780000000001</v>
+        <v>-90.2435</v>
       </c>
       <c r="E21" t="n">
-        <v>-57.6041</v>
+        <v>-52.7428</v>
       </c>
       <c r="F21" t="n">
-        <v>-39.9638</v>
+        <v>-37.5006</v>
       </c>
       <c r="G21" t="n">
         <v>-62.5861</v>
@@ -2092,13 +2092,13 @@
         <v>43.2494</v>
       </c>
       <c r="S21" t="n">
-        <v>-25.7295</v>
+        <v>-18.4052</v>
       </c>
       <c r="T21" t="n">
-        <v>-14.3542</v>
+        <v>-9.4931</v>
       </c>
       <c r="U21" t="n">
-        <v>-11.3754</v>
+        <v>-8.9123</v>
       </c>
       <c r="V21" t="n">
         <v>-9.6381</v>
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-508.6544000000001</v>
+        <v>-490.4489</v>
       </c>
       <c r="E22" t="n">
-        <v>-213.6468</v>
+        <v>-206.4736</v>
       </c>
       <c r="F22" t="n">
-        <v>-295.0070000000001</v>
+        <v>-283.9761</v>
       </c>
       <c r="G22" t="n">
         <v>-292.6652</v>
@@ -2146,7 +2146,7 @@
         <v>136.2427</v>
       </c>
       <c r="K22" t="n">
-        <v>41.86670000000001</v>
+        <v>41.8667</v>
       </c>
       <c r="L22" t="n">
         <v>94.3771</v>
@@ -2170,13 +2170,13 @@
         <v>344.644</v>
       </c>
       <c r="S22" t="n">
-        <v>-126.3339</v>
+        <v>-108.1278</v>
       </c>
       <c r="T22" t="n">
-        <v>-56.9154</v>
+        <v>-49.7411</v>
       </c>
       <c r="U22" t="n">
-        <v>-69.41850000000001</v>
+        <v>-58.3859</v>
       </c>
       <c r="V22" t="n">
         <v>-19.183</v>
